--- a/data/sars/alaska/tables/Alaska_2007_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2007_Appendix2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DC2EF9-F479-684D-B726-6D1EFFA1EE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEE13B7-7009-4342-8ED6-8C5B5F4B4B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="16880" windowHeight="21380" xr2:uid="{ABA5A89C-021C-B242-B0AA-C117CDB3CA48}"/>
   </bookViews>
@@ -2647,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="1">
-        <v>205</v>
+        <v>2005</v>
       </c>
       <c r="H37" s="1">
         <v>0.12</v>

--- a/data/sars/alaska/tables/Alaska_2007_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2007_Appendix2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEE13B7-7009-4342-8ED6-8C5B5F4B4B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA29145F-F666-4141-9FB3-86BB54068B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="16880" windowHeight="21380" xr2:uid="{ABA5A89C-021C-B242-B0AA-C117CDB3CA48}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="23660" windowHeight="21640" xr2:uid="{ABA5A89C-021C-B242-B0AA-C117CDB3CA48}"/>
   </bookViews>
   <sheets>
     <sheet name="tabula-Alaska_2007_Appendix2" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="75">
   <si>
     <t>Alaska</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>comments</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -393,7 +399,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -571,6 +577,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -734,7 +746,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -749,6 +761,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1126,17 +1147,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C97EA8-1CA8-BF48-B08D-80EB70201930}">
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="1" customWidth="1"/>
-    <col min="3" max="14" width="10.83203125" style="1"/>
-    <col min="15" max="15" width="10.83203125" style="2"/>
-    <col min="16" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="15" width="10.83203125" style="1"/>
+    <col min="16" max="16" width="10.83203125" style="2"/>
+    <col min="17" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
@@ -1180,10 +1201,13 @@
         <v>71</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>42</v>
       </c>
@@ -1218,7 +1242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1253,7 +1277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1297,7 +1321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1341,7 +1365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1385,7 +1409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1429,95 +1453,103 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="6">
         <v>302</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="6">
         <v>0.186</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="6">
         <v>264</v>
       </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="F8" s="7">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6">
         <v>2006</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="6">
         <v>0.04</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="6">
         <v>0.3</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1</v>
-      </c>
-      <c r="M8" s="1">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1" t="s">
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6">
+        <v>1</v>
+      </c>
+      <c r="M8" s="6">
+        <v>1</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="O8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P8" s="8"/>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="7">
         <v>10545</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="6">
         <v>0.13</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="7">
         <v>9472</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="7">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="6">
         <v>2001</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="6">
         <v>0.04</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="6">
         <v>0.5</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="6">
         <v>95</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="6">
         <v>0.2</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="6">
         <v>45</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="6">
         <v>46</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P9" s="8"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
@@ -1552,7 +1584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
@@ -1596,51 +1628,55 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="7">
         <v>5703</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7">
         <v>5703</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="7">
         <v>2</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="6">
         <v>2003</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="6">
         <v>0.04</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="6">
         <v>0.1</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="6">
         <v>11.4</v>
       </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1" t="s">
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" s="8"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1684,7 +1720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1727,11 +1763,11 @@
       <c r="N14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O14" s="5" t="s">
+      <c r="P14" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1775,7 +1811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -1819,7 +1855,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -1862,11 +1898,11 @@
       <c r="N17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O17" s="5" t="s">
+      <c r="P17" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -1909,11 +1945,11 @@
       <c r="N18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O18" s="5" t="s">
+      <c r="P18" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1956,137 +1992,149 @@
       <c r="N19" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O19" s="5" t="s">
+      <c r="P19" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="6">
         <v>394</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="6">
         <v>0.08</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="6">
         <v>367</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="6">
         <v>1999</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="6">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="6">
         <v>0.1</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="6">
         <v>1.3</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="6">
         <v>0.2</v>
       </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
+      <c r="L20" s="6">
+        <v>0</v>
+      </c>
+      <c r="M20" s="6">
         <v>0.2</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="N20" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="O20" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="7">
         <v>4005</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="6">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="7">
         <v>3698</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="7">
         <v>12</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="6">
         <v>1993</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="6">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="6">
         <v>0.1</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="6">
         <v>12.9</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="6">
         <v>3.2</v>
       </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
+      <c r="L21" s="6">
+        <v>0</v>
+      </c>
+      <c r="M21" s="6">
         <v>5</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="N21" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="O21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="6">
         <v>961</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="6">
         <v>0.12</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="6">
         <v>868</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="6">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="6">
         <v>0.1</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="6">
         <v>3</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="6">
         <v>1.4</v>
       </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
+      <c r="L22" s="6">
+        <v>0</v>
+      </c>
+      <c r="M22" s="6">
         <v>2.8</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N22" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -2130,7 +2178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -2168,45 +2216,49 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="6">
         <v>7</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D25" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6">
         <v>7</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="6">
         <v>0.04</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="6">
         <v>0.5</v>
       </c>
-      <c r="J25" s="1">
-        <v>0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1" t="s">
+      <c r="J25" s="6">
+        <v>0</v>
+      </c>
+      <c r="K25" s="6">
+        <v>0</v>
+      </c>
+      <c r="L25" s="6">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P25" s="8"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
@@ -2250,7 +2302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -2288,7 +2340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -2323,95 +2375,103 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1">
+      <c r="C29" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="6">
         <v>0.04</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29" s="6">
         <v>0.1</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1" t="s">
+      <c r="J29" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K29" s="6">
+        <v>0</v>
+      </c>
+      <c r="L29" s="6">
+        <v>0</v>
+      </c>
+      <c r="M29" s="6">
+        <v>0</v>
+      </c>
+      <c r="N29" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+      <c r="O29" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P29" s="8"/>
+    </row>
+    <row r="30" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="7">
         <v>721935</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="D30" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="7">
         <v>709881</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="7">
         <v>2</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="6">
         <v>2004</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="6">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="6">
         <v>0.5</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J30" s="7">
         <v>15262</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K30" s="6">
         <v>0.8</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L30" s="6">
         <v>702</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M30" s="6">
         <v>704</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="N30" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P30" s="8"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>45</v>
       </c>
@@ -2455,7 +2515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
@@ -2490,7 +2550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -2525,42 +2585,46 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1">
+      <c r="C34" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6">
         <v>0.04</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I34" s="6">
         <v>0.1</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
+      <c r="J34" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K34" s="6">
         <v>0.5</v>
       </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
+      <c r="L34" s="6">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6">
         <v>0.5</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="N34" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P34" s="8"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -2595,7 +2659,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>46</v>
       </c>
@@ -2630,87 +2694,95 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="7">
         <v>48519</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="7">
         <v>44584</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="7">
         <v>2</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" s="6">
         <v>2005</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="6">
         <v>0.12</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37" s="6">
         <v>0.75</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="7">
         <v>2006</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K37" s="6">
         <v>1.4</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L37" s="6">
         <v>9</v>
       </c>
-      <c r="M37" s="1">
+      <c r="M37" s="6">
         <v>15.8</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="N37" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+      <c r="O37" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P37" s="8"/>
+    </row>
+    <row r="38" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="7">
         <v>38988</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="7">
         <v>38988</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="7">
         <v>2</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="6">
         <v>2004</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="6">
         <v>0.12</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I38" s="6">
         <v>0.1</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="6">
         <v>234</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K38" s="6">
         <v>24.6</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L38" s="6">
         <v>198</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M38" s="6">
         <v>223.6</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="N38" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="O38" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P38" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
